--- a/공연공_Scope3_템플릿_수정본_v2 1_260805_v.0.2.xlsx
+++ b/공연공_Scope3_템플릿_수정본_v2 1_260805_v.0.2.xlsx
@@ -773,7 +773,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_APPLIED_COMPANY</formula1>
     </dataValidation>
   </dataValidations>
@@ -2747,10 +2747,10 @@
     <mergeCell ref="C18:C19"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D20:D220" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="드롭다운 값 확인" error="배출계수 DB 기준 드롭다운 목록에서 선택해 주세요." type="list">
+    <dataValidation sqref="D20:D220" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_ENERGY</formula1>
     </dataValidation>
-    <dataValidation sqref="E20:E220" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="드롭다운 값 확인" error="배출계수 DB 기준 드롭다운 목록에서 선택해 주세요." type="list">
+    <dataValidation sqref="E20:E220" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_ENERGY_UNIT</formula1>
     </dataValidation>
   </dataValidations>
@@ -5701,13 +5701,13 @@
     <mergeCell ref="I17:T17"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D19:D219" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="드롭다운 값 확인" error="배출계수 DB 기준 드롭다운 목록에서 선택해 주세요." type="list">
+    <dataValidation sqref="D19:D219" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_WASTE_C5_TYPE</formula1>
     </dataValidation>
-    <dataValidation sqref="F20:F219" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="드롭다운 값 확인" error="배출계수 DB 기준 드롭다운 목록에서 선택해 주세요." type="list">
+    <dataValidation sqref="F20:F219" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_WASTE_UNIT</formula1>
     </dataValidation>
-    <dataValidation sqref="G19:G219" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="드롭다운 값 확인" error="배출계수 DB 기준 드롭다운 목록에서 선택해 주세요." type="list">
+    <dataValidation sqref="G19:G219" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_WASTE_METHOD</formula1>
     </dataValidation>
   </dataValidations>
@@ -36645,7 +36645,7 @@
     <mergeCell ref="Y18:Y19"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D20:D665" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="드롭다운 값 확인" error="배출계수 DB 기준 드롭다운 목록에서 선택해 주세요." type="list">
+    <dataValidation sqref="D20:D665" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_TRAVEL_DISTANCE</formula1>
     </dataValidation>
   </dataValidations>
@@ -62221,10 +62221,10 @@
     <mergeCell ref="C19:C20"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D21:D221" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="드롭다운 값 확인" error="배출계수 DB 기준 드롭다운 목록에서 선택해 주세요." type="list">
+    <dataValidation sqref="D21:D221" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_TRAVEL_DISTANCE</formula1>
     </dataValidation>
-    <dataValidation sqref="D662:D761" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D662:D761" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_TRAVEL_DISTANCE</formula1>
     </dataValidation>
   </dataValidations>
@@ -63923,10 +63923,10 @@
     <mergeCell ref="C18:C19"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D20:D220" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="드롭다운 값 확인" error="배출계수 DB 기준 드롭다운 목록에서 선택해 주세요." type="list">
+    <dataValidation sqref="D20:D220" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_ENERGY</formula1>
     </dataValidation>
-    <dataValidation sqref="E21:E220" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="드롭다운 값 확인" error="배출계수 DB 기준 드롭다운 목록에서 선택해 주세요." type="list">
+    <dataValidation sqref="E21:E220" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값입니다" error="드롭다운 목록에 없는 값이에요. 목록에서 고르는 걸 권장하지만, 실제 상황에 맞는 다른 표현이 있다면 그대로 입력해도 괜찮습니다." type="list" errorStyle="warning">
       <formula1>DD_ENERGY_UNIT</formula1>
     </dataValidation>
   </dataValidations>
